--- a/rolodex/data/creative_ideas.xlsx
+++ b/rolodex/data/creative_ideas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tania/Dropbox/Scientific_Data_Insights_myownproject/rolodex/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tania/Dropbox/Scientific_Data_Insights_myownproject/oziblue/oziblue/rolodex/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E5095E-735B-0F4D-B1FF-FDFD6A7018CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873F8A79-3636-374C-B0DF-354F75FF4DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{B0F39D99-0CC5-DF42-8CF9-8A4441CB1024}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="99">
   <si>
     <t>idea</t>
   </si>
@@ -161,9 +161,6 @@
     <t>Domestika course</t>
   </si>
   <si>
-    <t>Paulina course (beta, tree, etc)</t>
-  </si>
-  <si>
     <t>Do the 100 day project</t>
   </si>
   <si>
@@ -267,13 +264,82 @@
   </si>
   <si>
     <t>Gesture sketching (i.e. only draw the big contours or major lines of an object or animal, and draw quickly and with wide gestures)</t>
+  </si>
+  <si>
+    <t>Paint Audubon birds</t>
+  </si>
+  <si>
+    <t>Find books and botanical illustrations on the Biodiversity Heritage Library</t>
+  </si>
+  <si>
+    <t>https://www.vogelwarte.ch/fr/</t>
+  </si>
+  <si>
+    <t>Paint birds, eg blue birds, birds of Switzerland</t>
+  </si>
+  <si>
+    <t>Paint birds of the world, birds in Cornell webcams</t>
+  </si>
+  <si>
+    <t>https://www.allaboutbirds.org/cams/</t>
+  </si>
+  <si>
+    <t>Paint fish species</t>
+  </si>
+  <si>
+    <t>https://www.audubon.org/art/birds-of-america</t>
+  </si>
+  <si>
+    <t>Explore Curtis Botanical Magazine</t>
+  </si>
+  <si>
+    <t>Explore archive of Curtis Botanical Magazine on BHL</t>
+  </si>
+  <si>
+    <t>https://www.biodiversitylibrary.org/bibliography/706</t>
+  </si>
+  <si>
+    <t>https://www.kew.org/science/our-science/publications-and-reports/publications/curtis-botanical-magazine</t>
+  </si>
+  <si>
+    <t>https://www.soc-botanical-artists.org/education/distance-learning-diploma-course/</t>
+  </si>
+  <si>
+    <t>Practice for Diploma of Society of Botanical Artists</t>
+  </si>
+  <si>
+    <t>Read and learn about botanical illustrators</t>
+  </si>
+  <si>
+    <t>Find inspiration on ten thousand villages</t>
+  </si>
+  <si>
+    <t>https://www.tenthousandvillages.com/</t>
+  </si>
+  <si>
+    <t>Paulina course (beta, trees, leaves, taller 30-dias, negative, alla Prima, etc)</t>
+  </si>
+  <si>
+    <t>Find idea in Sketchbook joy book by Katie Moody</t>
+  </si>
+  <si>
+    <t>Buy or pick flowers and paint bouquet alla prima</t>
+  </si>
+  <si>
+    <t>Create summaries of nature journaling material and information, translate english videos into French</t>
+  </si>
+  <si>
+    <t>Sushma Hegde watercolor tutorial</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QwRDj4hHkQI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -285,6 +351,13 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -311,9 +384,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -649,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C22599-7B30-4243-9864-0E94093364E9}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.1640625" bestFit="1" customWidth="1"/>
@@ -673,7 +747,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -787,7 +861,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -828,7 +902,7 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -900,7 +974,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
@@ -908,18 +982,18 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -927,7 +1001,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
         <v>31</v>
@@ -935,7 +1009,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -943,7 +1017,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
         <v>39</v>
@@ -951,7 +1025,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
         <v>39</v>
@@ -959,23 +1033,23 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
         <v>52</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -983,7 +1057,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -991,7 +1065,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -999,7 +1073,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -1007,7 +1081,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1015,31 +1089,31 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
@@ -1047,7 +1121,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
         <v>39</v>
@@ -1055,96 +1129,236 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>66</v>
       </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
       <c r="B50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>69</v>
-      </c>
-      <c r="B51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>70</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s">
         <v>71</v>
       </c>
-      <c r="B53" t="s">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>73</v>
       </c>
       <c r="B54" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>85</v>
+      </c>
+      <c r="B64" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" t="s">
+        <v>39</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>91</v>
+      </c>
+      <c r="B67" t="s">
+        <v>9</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C22" r:id="rId1" xr:uid="{96056828-2E52-234B-A1C0-B274BB5DCCF8}"/>
     <hyperlink ref="C29" r:id="rId2" xr:uid="{1DD3AE1F-5269-1A4C-A91E-2A55F6B02A78}"/>
+    <hyperlink ref="C58" r:id="rId3" xr:uid="{AA0F0203-B561-A646-8514-A1FB1F46DD1A}"/>
+    <hyperlink ref="B61" r:id="rId4" display="https://www.allaboutbirds.org/cams/" xr:uid="{60E917EB-B6E8-A442-ACDE-25B3552C3A24}"/>
+    <hyperlink ref="C59" r:id="rId5" xr:uid="{F71B5381-97A5-C143-8419-6E5EEFB87B72}"/>
+    <hyperlink ref="C61" r:id="rId6" xr:uid="{A0D7219D-A134-0541-9B22-C6C3173CB206}"/>
+    <hyperlink ref="C64" r:id="rId7" xr:uid="{4045481A-F32B-D147-96C2-72753800EBCE}"/>
+    <hyperlink ref="C63" r:id="rId8" xr:uid="{768CC263-96D7-9C4D-84CD-F9666554A2D4}"/>
+    <hyperlink ref="C65" r:id="rId9" xr:uid="{FEFB80FD-8EBE-4C4C-999B-107E36A962BA}"/>
+    <hyperlink ref="C67" r:id="rId10" xr:uid="{78D2CB8F-2AA7-1349-B7F4-342E4CAB6ADC}"/>
+    <hyperlink ref="C2" r:id="rId11" xr:uid="{346B6B47-7CF8-0E40-9203-95E75C087CF2}"/>
+    <hyperlink ref="C71" r:id="rId12" xr:uid="{D6446BAB-3AE7-1A4E-8E02-1103891DC781}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
